--- a/GPIpuget/project/Post Hopper Run Checks.xlsx
+++ b/GPIpuget/project/Post Hopper Run Checks.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -49,10 +49,7 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
+    <t>No missing bio or symbol files...</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -480,6 +477,26 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -493,34 +510,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -535,24 +532,24 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>
@@ -590,7 +587,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -608,166 +605,161 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>15</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>17</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>19</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>

--- a/GPIpuget/project/Post Hopper Run Checks.xlsx
+++ b/GPIpuget/project/Post Hopper Run Checks.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -49,7 +49,10 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>No missing bio or symbol files...</t>
+    <t>PEBBLEtiehi.bio</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi.v</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -477,7 +480,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -497,7 +500,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -517,7 +520,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -532,7 +535,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -547,7 +550,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -587,7 +590,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -605,6 +608,11 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -617,32 +625,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -657,19 +665,19 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -682,19 +690,19 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>16</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -707,19 +715,19 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>18</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -732,19 +740,19 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>20</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -757,7 +765,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Post Hopper Run Checks.xlsx
+++ b/GPIpuget/project/Post Hopper Run Checks.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -34,10 +34,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Your schematic contains no net zero.</t>
+    <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -480,6 +477,26 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -493,34 +510,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -535,22 +532,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -640,134 +637,134 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>15</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>17</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>19</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>

--- a/GPIpuget/project/Post Hopper Run Checks.xlsx
+++ b/GPIpuget/project/Post Hopper Run Checks.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -34,31 +34,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
+  </si>
+  <si>
+    <t>Validate no "text" in Datamaps</t>
+  </si>
+  <si>
+    <t>No errors</t>
+  </si>
+  <si>
+    <t>Missing Bio Symbol Files</t>
+  </si>
+  <si>
+    <t>No missing bio or symbol files...</t>
+  </si>
+  <si>
+    <t>Missing Nets</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
     <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
-  </si>
-  <si>
-    <t>Validate no "text" in Datamaps</t>
-  </si>
-  <si>
-    <t>No errors</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
-  </si>
-  <si>
-    <t>Missing Nets</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -587,7 +587,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -605,39 +605,34 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">

--- a/GPIpuget/project/Post Hopper Run Checks.xlsx
+++ b/GPIpuget/project/Post Hopper Run Checks.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -59,6 +59,12 @@
   </si>
   <si>
     <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XU6,trim_vbuffer_negative</t>
+  </si>
+  <si>
+    <t>XU6,trim_vbuffer_positive</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -477,7 +483,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -497,7 +503,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -517,7 +523,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -532,7 +538,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -547,7 +553,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -612,7 +618,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -645,6 +651,16 @@
         <v>12</v>
       </c>
     </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -657,17 +673,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -682,17 +698,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -707,17 +723,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -732,17 +748,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -757,7 +773,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Post Hopper Run Checks.xlsx
+++ b/GPIpuget/project/Post Hopper Run Checks.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -34,10 +34,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Your schematic contains no net zero.</t>
+    <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
@@ -56,15 +56,6 @@
   </si>
   <si>
     <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XU6,trim_vbuffer_negative</t>
-  </si>
-  <si>
-    <t>XU6,trim_vbuffer_positive</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -483,7 +474,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -503,7 +494,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -523,7 +514,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -538,7 +529,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -553,7 +544,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -618,7 +609,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -638,144 +629,134 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>16</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>18</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>

--- a/GPIpuget/project/Post Hopper Run Checks.xlsx
+++ b/GPIpuget/project/Post Hopper Run Checks.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -34,28 +34,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
+  </si>
+  <si>
+    <t>Validate no "text" in Datamaps</t>
+  </si>
+  <si>
+    <t>No errors</t>
+  </si>
+  <si>
+    <t>Missing Bio Symbol Files</t>
+  </si>
+  <si>
+    <t>No missing bio or symbol files...</t>
+  </si>
+  <si>
+    <t>Missing Nets</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
     <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
-  </si>
-  <si>
-    <t>Validate no "text" in Datamaps</t>
-  </si>
-  <si>
-    <t>No errors</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>No missing bio or symbol files...</t>
-  </si>
-  <si>
-    <t>Missing Nets</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -474,7 +477,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -494,7 +497,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -514,7 +517,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -529,7 +532,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +547,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -629,17 +632,17 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -654,19 +657,19 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -679,19 +682,19 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -704,19 +707,19 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>17</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -729,19 +732,19 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>19</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -754,7 +757,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
